--- a/Project_ETF/ETF_Investment_Portfolio/00713/ETF_Investment_Portfolio_20260630.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00713/ETF_Investment_Portfolio_20260630.xlsx
@@ -1107,17 +1107,17 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>2377</t>
+          <t>4766</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>微星</t>
+          <t>南寶</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>8,486,000</t>
+          <t>3,615,000</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
@@ -1129,17 +1129,17 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>4766</t>
+          <t>2377</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>南寶</t>
+          <t>微星</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>3,615,000</t>
+          <t>8,486,000</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -1327,17 +1327,17 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>2376</t>
+          <t>9939</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>技嘉</t>
+          <t>宏全</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>2,939,000</t>
+          <t>7,878,597</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -1349,17 +1349,17 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>1210</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>大成</t>
+          <t>技嘉</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>18,147,000</t>
+          <t>2,939,000</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
@@ -1371,17 +1371,17 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>9939</t>
+          <t>1210</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>宏全</t>
+          <t>大成</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>7,878,597</t>
+          <t>18,147,000</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
@@ -1547,17 +1547,17 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>1476</t>
+          <t>3036</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>儒鴻</t>
+          <t>文曄</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>2,572,000</t>
+          <t>3,785,000</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
@@ -1569,17 +1569,17 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>2504</t>
+          <t>1476</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>國產</t>
+          <t>儒鴻</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>24,248,000</t>
+          <t>2,572,000</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
@@ -1591,17 +1591,17 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>3036</t>
+          <t>2504</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>文曄</t>
+          <t>國產</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>3,785,000</t>
+          <t>24,248,000</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
@@ -1635,17 +1635,17 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>2882</t>
+          <t>2385</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>國泰金</t>
+          <t>群光</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>7,825,000</t>
+          <t>7,350,000</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
@@ -1657,17 +1657,17 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>2385</t>
+          <t>2882</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>群光</t>
+          <t>國泰金</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>7,350,000</t>
+          <t>7,825,000</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
